--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487453_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487453_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.3565</v>
+        <v>8.143000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6153</v>
+        <v>5.0967</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7413</v>
+        <v>3.0463</v>
       </c>
       <c r="G2" t="n">
         <v>5.23</v>
@@ -610,13 +610,13 @@
         <v>2.9377</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5966</v>
+        <v>1.383</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6148</v>
+        <v>1.0963</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9817</v>
+        <v>0.2867</v>
       </c>
       <c r="V2" t="n">
         <v>0.5507</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.0876</v>
+        <v>6.5345</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9052</v>
+        <v>4.7531</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1823</v>
+        <v>1.7814</v>
       </c>
       <c r="G3" t="n">
         <v>1.0134</v>
@@ -688,13 +688,13 @@
         <v>3.1336</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3911</v>
+        <v>0.8379</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8556</v>
+        <v>0.7034</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5355</v>
+        <v>0.1345</v>
       </c>
       <c r="V3" t="n">
         <v>1.5495</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4811</v>
+        <v>6.0244</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8219</v>
+        <v>6.2048</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3408</v>
+        <v>-0.1804</v>
       </c>
       <c r="G4" t="n">
         <v>5.1848</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1005</v>
+        <v>0.6437</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4029</v>
+        <v>0.7857</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3024</v>
+        <v>-0.142</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4019</v>
+        <v>3.8877</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1136</v>
+        <v>1.8765</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2883</v>
+        <v>2.0112</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6026</v>
+        <v>3.7212</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7639</v>
+        <v>0.7349</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8387</v>
+        <v>2.9863</v>
       </c>
       <c r="J5" t="n">
-        <v>2.987</v>
+        <v>3.8327</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0326</v>
+        <v>1.0037</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9544</v>
+        <v>2.8291</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3844</v>
+        <v>-0.1115</v>
       </c>
       <c r="N5" t="n">
         <v>-0.2687</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1157</v>
+        <v>0.1572</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9585</v>
+        <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0954</v>
+        <v>0.2448</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1059</v>
+        <v>0.6681</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0105</v>
+        <v>-0.4233</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2754</v>
+        <v>-0.6659</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0609</v>
+        <v>3.6673</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4507</v>
+        <v>2.5394</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6102</v>
+        <v>1.1279</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7212</v>
+        <v>2.6026</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7349</v>
+        <v>0.7639</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9863</v>
+        <v>1.8387</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8327</v>
+        <v>2.987</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0037</v>
+        <v>1.0326</v>
       </c>
       <c r="L6" t="n">
-        <v>2.8291</v>
+        <v>1.9544</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1115</v>
+        <v>-0.3844</v>
       </c>
       <c r="N6" t="n">
         <v>-0.2687</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1572</v>
+        <v>-0.1157</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>2.546</v>
+        <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.582</v>
+        <v>0.3608</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2423</v>
+        <v>0.5317</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8243</v>
+        <v>-0.1708</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6659</v>
+        <v>-0.2754</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3385</v>
+        <v>2.9943</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3541</v>
+        <v>0.8228</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9844</v>
+        <v>2.1715</v>
       </c>
       <c r="G7" t="n">
         <v>0.416</v>
@@ -1000,13 +1000,13 @@
         <v>2.7419</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0568</v>
+        <v>-0.401</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7722</v>
+        <v>-0.3035</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2846</v>
+        <v>-0.0975</v>
       </c>
       <c r="V7" t="n">
         <v>1.2166</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3359</v>
+        <v>2.1966</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4063</v>
+        <v>1.3205</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9296</v>
+        <v>0.8761</v>
       </c>
       <c r="G8" t="n">
         <v>0.0214</v>
@@ -1078,13 +1078,13 @@
         <v>1.9585</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3561</v>
+        <v>0.2167</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7287</v>
+        <v>0.6428</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3726</v>
+        <v>-0.4261</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6435999999999999</v>
+        <v>0.2509</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2224</v>
+        <v>0.6722</v>
       </c>
       <c r="F9" t="n">
         <v>-0.4213</v>
@@ -1156,10 +1156,10 @@
         <v>2.9377</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2763</v>
+        <v>-0.3817</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.891</v>
+        <v>0.0035</v>
       </c>
       <c r="U9" t="n">
         <v>-0.3852</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9634</v>
+        <v>0.1717</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4273</v>
+        <v>-0.5327</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4639</v>
+        <v>0.7045</v>
       </c>
       <c r="G10" t="n">
         <v>-0.802</v>
@@ -1234,13 +1234,13 @@
         <v>2.7419</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5911</v>
+        <v>-0.456</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9328</v>
+        <v>-0.0382</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6583</v>
+        <v>-0.4177</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3329</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5619</v>
+        <v>-1.8793</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9047</v>
+        <v>-2.436</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3428</v>
+        <v>0.5567</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3335</v>
@@ -1312,13 +1312,13 @@
         <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4242</v>
+        <v>-0.7416</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6358</v>
+        <v>-0.167</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7885</v>
+        <v>-0.5746</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3385</v>
+        <v>-3.951</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.917</v>
+        <v>-3.6365</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4215</v>
+        <v>-0.3145</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6174</v>
@@ -1390,13 +1390,13 @@
         <v>2.1543</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6415</v>
+        <v>-0.2541</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0306</v>
+        <v>0.25</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.611</v>
+        <v>-0.504</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2754</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>26.555</v>
+        <v>28.0401</v>
       </c>
       <c r="E13" t="n">
-        <v>15.1957</v>
+        <v>16.6808</v>
       </c>
       <c r="F13" t="n">
-        <v>11.3592</v>
+        <v>11.3594</v>
       </c>
       <c r="G13" t="n">
         <v>11.0726</v>
@@ -1468,13 +1468,13 @@
         <v>25.4603</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.03219999999999934</v>
+        <v>1.4525</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6878</v>
+        <v>4.172800000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.7202</v>
+        <v>-2.72</v>
       </c>
       <c r="V13" t="n">
         <v>0.826</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3758</v>
+        <v>0.0704</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5446</v>
+        <v>1.8516</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9204</v>
+        <v>-1.7812</v>
       </c>
       <c r="G14" t="n">
         <v>0.8779</v>
@@ -1546,13 +1546,13 @@
         <v>2.1543</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0009</v>
+        <v>0.4471</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1941</v>
+        <v>0.5011</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1932</v>
+        <v>-0.054</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2754</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4283</v>
+        <v>0.0419</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0404</v>
+        <v>0.3474</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4687</v>
+        <v>-0.3055</v>
       </c>
       <c r="G15" t="n">
         <v>0.9208</v>
@@ -1624,13 +1624,13 @@
         <v>0.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4862</v>
+        <v>-0.016</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.297</v>
+        <v>0.01</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1892</v>
+        <v>-0.026</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.124</v>
+        <v>-1.065</v>
       </c>
       <c r="E16" t="n">
         <v>-2.121</v>
       </c>
       <c r="F16" t="n">
-        <v>0.997</v>
+        <v>1.056</v>
       </c>
       <c r="G16" t="n">
         <v>1.2611</v>
@@ -1702,13 +1702,13 @@
         <v>1.7626</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9443</v>
+        <v>1.0034</v>
       </c>
       <c r="T16" t="n">
         <v>0.6516</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2927</v>
+        <v>0.3517</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9149</v>
+        <v>-1.7056</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7071</v>
+        <v>-1.6047</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2078</v>
+        <v>-0.1009</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4964</v>
@@ -1780,13 +1780,13 @@
         <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4392</v>
+        <v>-0.23</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2016</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1911</v>
+        <v>-2.9324</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4843</v>
+        <v>-0.7438</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6753</v>
+        <v>-2.1886</v>
       </c>
       <c r="G18" t="n">
         <v>-2.3424</v>
@@ -1858,13 +1858,13 @@
         <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>1.21</v>
+        <v>0.4687</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9567</v>
+        <v>0.7287</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7467</v>
+        <v>-0.26</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2754</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6334</v>
+        <v>-3.1718</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9419</v>
+        <v>1.4303</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.5753</v>
+        <v>-4.602</v>
       </c>
       <c r="G19" t="n">
         <v>-1.716</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2198</v>
+        <v>-0.3186</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6693</v>
+        <v>0.1576</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4495</v>
+        <v>-0.4762</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9412</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3837</v>
+        <v>-4.2371</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8469</v>
+        <v>-3.5399</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.6972</v>
       </c>
       <c r="G20" t="n">
         <v>-3.6539</v>
@@ -2014,13 +2014,13 @@
         <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1422</v>
+        <v>0.0044</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.22</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.2351</v>
+        <v>-5.2542</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8119</v>
+        <v>-3.5049</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4232</v>
+        <v>-1.7494</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2155</v>
@@ -2092,13 +2092,13 @@
         <v>2.1543</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0266</v>
+        <v>-0.0457</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1347</v>
+        <v>0.4417</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1613</v>
+        <v>-0.4874</v>
       </c>
       <c r="V21" t="n">
         <v>1.8825</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.2687</v>
+        <v>-6.9368</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8836</v>
+        <v>-3.4742</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3851</v>
+        <v>-3.4625</v>
       </c>
       <c r="G22" t="n">
         <v>-4.7081</v>
@@ -2170,13 +2170,13 @@
         <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2484</v>
+        <v>0.0835</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1317</v>
+        <v>0.2776</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1167</v>
+        <v>-0.1941</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9412</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-26.555</v>
+        <v>-25.1906</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.3593</v>
+        <v>-11.3592</v>
       </c>
       <c r="F23" t="n">
-        <v>-15.1956</v>
+        <v>-13.8313</v>
       </c>
       <c r="G23" t="n">
         <v>-11.0725</v>
@@ -2248,13 +2248,13 @@
         <v>10.7715</v>
       </c>
       <c r="S23" t="n">
-        <v>0.03239999999999998</v>
+        <v>1.3968</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7201</v>
+        <v>2.72</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.6877</v>
+        <v>-1.3233</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8261000000000001</v>
